--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.7941176470588235</v>
+        <v>0.8837209302325582</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4316546762589928</v>
+        <v>0.5915492957746479</v>
       </c>
       <c r="D2">
-        <v>0.7452830188679245</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F2">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8837209302325582</v>
+        <v>0.8780487804878049</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5915492957746479</v>
+        <v>0.5633802816901409</v>
       </c>
       <c r="D2">
-        <v>0.6041666666666666</v>
+        <v>0.6326530612244898</v>
       </c>
       <c r="E2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G2">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
